--- a/output/pdf_financials_xlsx/DIG.H.xlsx
+++ b/output/pdf_financials_xlsx/DIG.H.xlsx
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001538</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002249</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.318785</v>
+        <v>-0.320323</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.07449600000000001</v>
+        <v>-0.07674499999999999</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.301147</v>
+        <v>-0.302685</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.061937</v>
+        <v>-0.06418600000000001</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-512.4772390790123</v>
+        <v>-515.0945322737097</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-72.64825936004505</v>
+        <v>-75.28619686590973</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -48786,7 +48786,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">

--- a/output/pdf_financials_xlsx/DIG.H.xlsx
+++ b/output/pdf_financials_xlsx/DIG.H.xlsx
@@ -558,15 +558,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0.123793</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0.048453</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0.058763</v>
@@ -641,15 +637,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -724,15 +716,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0.123793</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.048453</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0.058763</v>
@@ -807,15 +795,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -890,15 +874,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -973,15 +953,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -1056,15 +1032,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.557961</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.376646</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.379086</v>
@@ -1139,15 +1111,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.434168</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-0.328193</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-0.320323</v>
@@ -1222,15 +1190,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0.008946000000000001</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.004578</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.001538</v>
@@ -1305,15 +1269,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -1388,15 +1348,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -1471,15 +1427,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -1554,15 +1506,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.425222</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.323615</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.318785</v>
@@ -1637,15 +1585,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1894,15 +1838,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.425222</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.323615</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.318785</v>
@@ -1977,15 +1917,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -2060,15 +1996,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -2143,15 +2075,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.425222</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-0.323615</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.318785</v>
@@ -2206,15 +2134,11 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>-0.025</v>
@@ -2289,15 +2213,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>-0.025</v>
@@ -2372,15 +2292,11 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>4.25222</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>10.787167</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>12.7514</v>
@@ -2457,15 +2373,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.434168</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.328193</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.320323</v>
@@ -2540,15 +2452,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0.131206</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.048612</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.017638</v>
@@ -2623,15 +2531,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.302962</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.279581</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.302685</v>
@@ -2706,15 +2610,11 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>-244.7327393309799</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-577.0148391224485</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-515.0945322737097</v>
@@ -2789,15 +2689,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -2872,15 +2768,11 @@
           <t>Net Margin %</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="3" t="n">
+        <v>-343.4943817501797</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>-667.8946608053164</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>-542.4927250140395</v>
@@ -3302,22 +3194,22 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.002934</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.003342</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.004726</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.001885</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.0097</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.002966</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3357,22 +3249,22 @@
         <v>0.014776</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.026411</v>
+        <v>0.029345</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.025104</v>
+        <v>0.028446</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.027183</v>
+        <v>0.031909</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.002548</v>
+        <v>0.004433</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.027423</v>
+        <v>0.037123</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.000596</v>
+        <v>0.003562</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0.019759</v>
@@ -3742,22 +3634,22 @@
         <v>0.01792</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.02298</v>
+        <v>0.020046</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.023225</v>
+        <v>0.019883</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.01787</v>
+        <v>0.013144</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.013792</v>
+        <v>0.011907</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002206</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -4847,43 +4739,43 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.286299</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.308207</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.355332</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0295</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.029816</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.06300600000000001</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.004904</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.004904</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.030938</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.032199</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.018904</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.018904</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.057748</v>
       </c>
     </row>
     <row r="68">
@@ -6655,18 +6547,14 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.425222</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.323615</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-0.318785</v>
+        <v>-0.36728</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-0.07449600000000001</v>
@@ -6718,15 +6606,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -6777,15 +6661,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -6836,15 +6716,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>0</v>
@@ -6895,15 +6771,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0</v>
@@ -6954,15 +6826,11 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>0</v>
@@ -7013,15 +6881,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>0</v>
@@ -7072,15 +6936,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.140797</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.03621</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.038606</v>
@@ -7131,15 +6991,11 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>0</v>
@@ -7190,15 +7046,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
@@ -7249,15 +7101,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>0</v>
@@ -7308,36 +7156,32 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0.013171</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0.013394</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.007847</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.003574</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.002187</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.00105</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.00113</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>-0.011512</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -7367,15 +7211,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7426,15 +7266,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -7485,15 +7321,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>0</v>
@@ -7544,15 +7376,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -7603,15 +7431,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -7662,15 +7486,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -7721,15 +7541,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>0</v>
@@ -7780,15 +7596,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -7926,15 +7738,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -7985,15 +7793,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -8044,15 +7848,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>0</v>
@@ -8103,15 +7903,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -8162,15 +7958,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -8221,15 +8013,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -8280,15 +8068,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>0</v>
@@ -8426,15 +8210,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>0</v>
@@ -8572,15 +8352,11 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.01055</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.058409</v>
       </c>
       <c r="D130" s="3" t="n">
         <v>0.000612</v>
@@ -8631,15 +8407,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>0</v>
@@ -8690,15 +8462,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.047859</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.057797</v>
       </c>
       <c r="D132" s="3" t="n">
         <v>0.039556</v>
@@ -8749,15 +8517,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.058409</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.000612</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>0.040168</v>
@@ -8808,15 +8572,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -8959,7 +8719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T431"/>
+  <dimension ref="A1:T446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -35010,7 +34770,11 @@
           <t>Net loss from continuing operation $</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -36603,15 +36367,11 @@
           <t>BeginningCashPosition</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E293" s="5" t="n">
+        <v>0.01055</v>
+      </c>
+      <c r="F293" s="5" t="n">
+        <v>0.058409</v>
       </c>
       <c r="G293" s="5" t="n">
         <v>0.000612</v>
@@ -36677,15 +36437,11 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E294" s="5" t="n">
+        <v>0.058409</v>
+      </c>
+      <c r="F294" s="5" t="n">
+        <v>0.000612</v>
       </c>
       <c r="G294" s="5" t="n">
         <v>0.040168</v>
@@ -43151,15 +42907,11 @@
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E362" s="5" t="n">
+        <v>0.016696</v>
+      </c>
+      <c r="F362" s="5" t="n">
+        <v>0.073322</v>
       </c>
       <c r="G362" s="5" t="n">
         <v>-0.02678</v>
@@ -44588,7 +44340,11 @@
           <t>Accretion (note 12)</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -45348,16 +45104,16 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
+      <c r="E385" s="5" t="n">
+        <v>0.013171</v>
+      </c>
+      <c r="F385" s="5" t="n">
+        <v>0.013394</v>
       </c>
       <c r="G385" s="5" t="n">
         <v>0.007847</v>
@@ -46023,15 +45779,11 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E392" s="5" t="n">
+        <v>0.131206</v>
+      </c>
+      <c r="F392" s="5" t="n">
+        <v>0.048612</v>
       </c>
       <c r="G392" s="5" t="n">
         <v>0.017638</v>
@@ -46395,15 +46147,11 @@
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E396" s="5" t="n">
+        <v>-0.280845</v>
+      </c>
+      <c r="F396" s="5" t="n">
+        <v>-0.291914</v>
       </c>
       <c r="G396" s="5" t="n">
         <v>-0.246215</v>
@@ -46769,15 +46517,11 @@
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E400" s="5" t="n">
+        <v>-0.009593000000000001</v>
+      </c>
+      <c r="F400" s="5" t="n">
+        <v>0.092907</v>
       </c>
       <c r="G400" s="5" t="n">
         <v>-0.043035</v>
@@ -47925,15 +47669,11 @@
           <t>ChangeInWorkingCapital</t>
         </is>
       </c>
-      <c r="E412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E412" s="5" t="n">
+        <v>0.140797</v>
+      </c>
+      <c r="F412" s="5" t="n">
+        <v>0.03621</v>
       </c>
       <c r="G412" s="5" t="n">
         <v>0.038606</v>
@@ -48211,15 +47951,11 @@
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E415" s="5" t="n">
+        <v>-0.026289</v>
+      </c>
+      <c r="F415" s="5" t="n">
+        <v>-0.005415</v>
       </c>
       <c r="G415" s="5" t="n">
         <v>-0.016255</v>
@@ -48389,35 +48125,37 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Oil and gas $</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr"/>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E417" s="5" t="n">
+        <v>-0.425222</v>
+      </c>
+      <c r="F417" s="5" t="n">
+        <v>-0.323615</v>
       </c>
       <c r="G417" s="5" t="n">
-        <v>0.070147</v>
-      </c>
-      <c r="H417" s="5" t="n">
-        <v>0.093526</v>
+        <v>-0.36728</v>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
@@ -48483,17 +48221,17 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Royalties</t>
+          <t>Gain on liability settlement (note 4)</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
@@ -48502,16 +48240,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G418" s="5" t="n">
-        <v>-0.011384</v>
-      </c>
-      <c r="H418" s="5" t="n">
-        <v>-0.00827</v>
+      <c r="F418" s="5" t="n">
+        <v>-0.030305</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
@@ -48577,39 +48317,33 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Revenues total</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Promissory notes payable</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" s="5" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="F419" s="5" t="n">
+        <v>0.105</v>
       </c>
       <c r="G419" s="5" t="n">
-        <v>0.058763</v>
-      </c>
-      <c r="H419" s="5" t="n">
-        <v>0.085256</v>
+        <v>0.008</v>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
@@ -48675,17 +48409,17 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Gain on disposal of property, plant and equipment (note 9)</t>
+          <t>Issuance of common shares and warrants</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -48699,13 +48433,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H420" s="5" t="n">
-        <v>0.241656</v>
+      <c r="G420" s="5" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
@@ -48771,39 +48505,37 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Investing</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Proceeds on sale of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G421" s="5" t="n">
-        <v>0.001538</v>
-      </c>
-      <c r="H421" s="5" t="n">
-        <v>0.002249</v>
+      <c r="F421" s="5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
@@ -48869,35 +48601,37 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Operating</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E422" s="5" t="n">
+        <v>0.047859</v>
+      </c>
+      <c r="F422" s="5" t="n">
+        <v>-0.057797</v>
       </c>
       <c r="G422" s="5" t="n">
-        <v>0.068865</v>
-      </c>
-      <c r="H422" s="5" t="n">
-        <v>0.062801</v>
+        <v>0.039556</v>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
@@ -48963,22 +48697,22 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Interest paid $</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>InterestPaidSupplementalData</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -48991,11 +48725,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G423" s="5" t="n">
-        <v>0.237624</v>
-      </c>
-      <c r="H423" s="5" t="n">
-        <v>0.269488</v>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -49066,30 +48804,26 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Accretion</t>
+          <t>Oil and gas $</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E424" s="5" t="n">
+        <v>0.147283</v>
+      </c>
+      <c r="F424" s="5" t="n">
+        <v>0.056666</v>
       </c>
       <c r="G424" s="5" t="n">
-        <v>0.007847</v>
+        <v>0.070147</v>
       </c>
       <c r="H424" s="5" t="n">
-        <v>0.003574</v>
+        <v>0.093526</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -49160,34 +48894,26 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Depletion and depreciation</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Royalties</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" s="5" t="n">
+        <v>-0.02349</v>
+      </c>
+      <c r="F425" s="5" t="n">
+        <v>-0.008213</v>
       </c>
       <c r="G425" s="5" t="n">
-        <v>0.017638</v>
+        <v>-0.011384</v>
       </c>
       <c r="H425" s="5" t="n">
-        <v>0.012559</v>
+        <v>-0.00827</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -49258,30 +48984,30 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Other interest</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Revenues total</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E426" s="5" t="n">
+        <v>0.123793</v>
+      </c>
+      <c r="F426" s="5" t="n">
+        <v>0.048453</v>
       </c>
       <c r="G426" s="5" t="n">
-        <v>0.003852</v>
+        <v>0.058763</v>
       </c>
       <c r="H426" s="5" t="n">
-        <v>0.007655</v>
+        <v>0.085256</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -49352,12 +49078,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Interest on convertible debentures</t>
+          <t>Gain on disposal of property, plant and equipment (note 9)</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
@@ -49371,11 +49097,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G427" s="5" t="n">
-        <v>0.04326</v>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H427" s="5" t="n">
-        <v>0.04758</v>
+        <v>0.241656</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -49446,34 +49174,30 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E428" s="5" t="n">
+        <v>0.008946000000000001</v>
+      </c>
+      <c r="F428" s="5" t="n">
+        <v>0.004578</v>
       </c>
       <c r="G428" s="5" t="n">
-        <v>0.379086</v>
+        <v>0.001538</v>
       </c>
       <c r="H428" s="5" t="n">
-        <v>0.403657</v>
+        <v>0.002249</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -49549,29 +49273,21 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Operating</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" s="5" t="n">
+        <v>0.086546</v>
+      </c>
+      <c r="F429" s="5" t="n">
+        <v>0.059377</v>
       </c>
       <c r="G429" s="5" t="n">
-        <v>-0.318785</v>
+        <v>0.068865</v>
       </c>
       <c r="H429" s="5" t="n">
-        <v>-0.07449600000000001</v>
+        <v>0.062801</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
@@ -49647,12 +49363,12 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted (note 16)</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -49666,10 +49382,10 @@
         </is>
       </c>
       <c r="G430" s="5" t="n">
-        <v>-2.5e-08</v>
+        <v>0.237624</v>
       </c>
       <c r="H430" s="5" t="n">
-        <v>-5e-09</v>
+        <v>0.269488</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
@@ -49745,86 +49461,1508 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
+          <t>Accretion</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G431" s="5" t="n">
+        <v>0.007847</v>
+      </c>
+      <c r="H431" s="5" t="n">
+        <v>0.003574</v>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Depletion and depreciation</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E432" s="5" t="n">
+        <v>0.131206</v>
+      </c>
+      <c r="F432" s="5" t="n">
+        <v>0.048612</v>
+      </c>
+      <c r="G432" s="5" t="n">
+        <v>0.017638</v>
+      </c>
+      <c r="H432" s="5" t="n">
+        <v>0.012559</v>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Other interest</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" s="5" t="n">
+        <v>0.011277</v>
+      </c>
+      <c r="F433" s="5" t="n">
+        <v>0.002942</v>
+      </c>
+      <c r="G433" s="5" t="n">
+        <v>0.003852</v>
+      </c>
+      <c r="H433" s="5" t="n">
+        <v>0.007655</v>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Interest on convertible debentures</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F434" s="5" t="n">
+        <v>0.042687</v>
+      </c>
+      <c r="G434" s="5" t="n">
+        <v>0.04326</v>
+      </c>
+      <c r="H434" s="5" t="n">
+        <v>0.04758</v>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E435" s="5" t="n">
+        <v>0.557961</v>
+      </c>
+      <c r="F435" s="5" t="n">
+        <v>0.376646</v>
+      </c>
+      <c r="G435" s="5" t="n">
+        <v>0.379086</v>
+      </c>
+      <c r="H435" s="5" t="n">
+        <v>0.403657</v>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G436" s="5" t="n">
+        <v>-0.318785</v>
+      </c>
+      <c r="H436" s="5" t="n">
+        <v>-0.07449600000000001</v>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted (note 16)</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G437" s="5" t="n">
+        <v>-2.5e-08</v>
+      </c>
+      <c r="H437" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
           <t>Weighted average number of shares outstanding (note 16)</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr">
+      <c r="D438" t="inlineStr">
         <is>
           <t>BasicAverageShares</t>
         </is>
       </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G431" s="5" t="n">
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G438" s="5" t="n">
         <v>12.9584</v>
       </c>
-      <c r="H431" s="5" t="n">
+      <c r="H438" s="5" t="n">
         <v>15.552865</v>
       </c>
-      <c r="I431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T431" t="inlineStr">
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>General and administration</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E439" s="5" t="n">
+        <v>0.240704</v>
+      </c>
+      <c r="F439" s="5" t="n">
+        <v>0.239939</v>
+      </c>
+      <c r="G439" s="5" t="n">
+        <v>0.237624</v>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Accretion (note 5)</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" s="5" t="n">
+        <v>0.013171</v>
+      </c>
+      <c r="F440" s="5" t="n">
+        <v>0.013394</v>
+      </c>
+      <c r="G440" s="5" t="n">
+        <v>0.014998</v>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Gain on liability settlement (note 4)</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F441" s="5" t="n">
+        <v>-0.030305</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E442" s="5" t="n">
+        <v>-0.425222</v>
+      </c>
+      <c r="F442" s="5" t="n">
+        <v>-0.323615</v>
+      </c>
+      <c r="G442" s="5" t="n">
+        <v>-0.36728</v>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of year</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" s="5" t="n">
+        <v>-13.109748</v>
+      </c>
+      <c r="F443" s="5" t="n">
+        <v>-13.53497</v>
+      </c>
+      <c r="G443" s="5" t="n">
+        <v>-13.858585</v>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Deficit, end of year                                              $(14,225,865)     $(13,858,585)</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted (note 10) $</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F444" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="G444" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Interest on convertible debentures (note 8)</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" s="5" t="n">
+        <v>0.075057</v>
+      </c>
+      <c r="F445" s="5" t="n">
+        <v>0.042687</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Deficit, end of year                                              $(13,858,585)     $(13,534,970)</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted (note 10) $</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E446" s="5" t="n">
+        <v>-1e-07</v>
+      </c>
+      <c r="F446" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
         <is>
           <t>-</t>
         </is>
